--- a/ids540_specific/class_schedule_540_xlsx.xlsx
+++ b/ids540_specific/class_schedule_540_xlsx.xlsx
@@ -176,7 +176,7 @@
 - `Views and Copies Recap &lt;../notebooks/class_2/week_3/12_views_and_copies_recap.html&gt;`_
 **Additional Concepts**
 - `Numbers in Computers &lt;../notebooks/PDS_not_yet_in_coursera/20_programming_concepts/ints_and_floats.html&gt;`_
-- `Writing Good Notebooks &lt;../notebooks/PDS_not_yet_in_coursera/20_programming_concepts/writing_good_jupyter_notebooks.html&gt;`_</t>
+- `Writing Good Notebooks &lt;https://dukemids.com/data_science_skills/writing_good_jupyter_notebooks.html&gt;`_</t>
   </si>
   <si>
     <t>- `Ex 1 &lt;../exercises/exercise_numpy_viewcopies.html&gt;`_

--- a/ids540_specific/class_schedule_540_xlsx.xlsx
+++ b/ids540_specific/class_schedule_540_xlsx.xlsx
@@ -8,19 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vesper/Documents/GitHub/practicaldatascience_book/ids540_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A1787B-6FEF-F34C-8873-FB9B294DBA11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B0D3BC-518E-6149-B3D6-2F307193F018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37540" yWindow="600" windowWidth="34560" windowHeight="19360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="class_schedule_590" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="101">
   <si>
     <t>Date, Rm</t>
   </si>
@@ -85,9 +97,6 @@
     <t>Mon, Sep 7</t>
   </si>
   <si>
-    <t>- Lists In Depth</t>
-  </si>
-  <si>
     <t>- `Debugging (principles) &lt;../notebooks/PDS_not_yet_in_coursera/20_programming_concepts/10_debugging_principles.html&gt;`_
 - `Debugging (tools) &lt;../notebooks/PDS_not_yet_in_coursera/20_programming_concepts/20_debugging_in_vscode.html&gt;`_</t>
   </si>
@@ -101,9 +110,6 @@
     <t>- Buffer Day</t>
   </si>
   <si>
-    <t>- PPF3, Approaches to Testing. *Do do Coursera exercises in this section!*</t>
-  </si>
-  <si>
     <t>- `Blackjack &lt;../exercises/35_blackjack.html&gt;`_</t>
   </si>
   <si>
@@ -113,18 +119,12 @@
     <t>- List Practice</t>
   </si>
   <si>
-    <t xml:space="preserve">- PPF4, Diving Deeper with Lists (both Looking More into Lists and Heart Rate: An Example) </t>
-  </si>
-  <si>
     <t>- `List Max &lt;../exercises/40_listmax.html&gt;`_</t>
   </si>
   <si>
     <t>Wed, Sep 16</t>
   </si>
   <si>
-    <t>- More Lists</t>
-  </si>
-  <si>
     <t>- `HR Peak &lt;../exercises/50_heartrate_peak.html&gt;`_</t>
   </si>
   <si>
@@ -132,10 +132,6 @@
   </si>
   <si>
     <t>- Object Oriented Programming</t>
-  </si>
-  <si>
-    <t>- `Join class session for next Coursera course with Duke email &lt;https://coursera.org/groups/numpy-data-science-kfkep/invitation&gt;`_
-- DSwithNSD1, Basics of Object Oriented Programming</t>
   </si>
   <si>
     <t>- `Point &lt;../exercises/60_point.html&gt;`_
@@ -396,12 +392,25 @@
 - `Max &lt;../exercises/exercises/20_max.html&gt;`_
 - `Triangle &lt;../exercises/exercises/30_triangle.html&gt;`_</t>
   </si>
+  <si>
+    <t>- PPF3, Validating Your Code. *Do do Coursera exercises in this section!*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- PPF4, Diving Deeper with Lists (all sub-modules) </t>
+  </si>
+  <si>
+    <t>- No new readings</t>
+  </si>
+  <si>
+    <t>- `Join class session for next Coursera course (DSwithNSD) with Duke email &lt;https://coursera.org/groups/numpy-data-science-kfkep/invitation&gt;`_
+- DSwithNSD1, Basics of Object Oriented Programming</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -413,26 +422,20 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Fira Code"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -455,36 +458,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -804,387 +800,397 @@
   <cols>
     <col min="1" max="1" width="33.1640625" customWidth="1"/>
     <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="105.5" style="5" customWidth="1"/>
+    <col min="3" max="3" width="105.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="57.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="139" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="1:4" ht="204" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="11"/>
+    </row>
+    <row r="5" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="7"/>
-    </row>
-    <row r="3" spans="1:4" ht="204" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="10" t="s">
+      <c r="D8" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="118" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="11"/>
+    </row>
+    <row r="10" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="9" t="s">
+      <c r="D10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="118" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="9" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="11" t="s">
+      <c r="C11" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="9" t="s">
+    </row>
+    <row r="12" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="D12" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="9" t="s">
+    </row>
+    <row r="13" spans="1:4" ht="136" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="11" t="s">
+      <c r="B13" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D13" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="9" t="s">
+    <row r="14" spans="1:4" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="136" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="9" t="s">
+      <c r="D14" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="170" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
+      <c r="C15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
+    </row>
+    <row r="17" spans="1:4" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="170" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="9" t="s">
+      <c r="D17" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C18" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="68" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="9" t="s">
+      <c r="C19" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="9" t="s">
+      <c r="C20" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="106" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="9" t="s">
+      <c r="C21" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="140" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="106" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="9" t="s">
+      <c r="C22" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="57" x14ac:dyDescent="0.2">
+      <c r="A23" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="140" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="9" t="s">
+      <c r="C23" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="134" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="60" x14ac:dyDescent="0.2">
-      <c r="A23" s="9" t="s">
+      <c r="C24" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="11"/>
+    </row>
+    <row r="25" spans="1:4" ht="103" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="134" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="9" t="s">
+    </row>
+    <row r="26" spans="1:4" ht="105" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="103" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="9" t="s">
+      <c r="C26" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="43" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="105" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="9" t="s">
+      <c r="C27" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="43" x14ac:dyDescent="0.2">
+      <c r="A28" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="43" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="9" t="s">
+      <c r="C28" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="11"/>
+      <c r="B29" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="43" x14ac:dyDescent="0.2">
-      <c r="A28" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B29" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="C29" s="11"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ids540_specific/class_schedule_540_xlsx.xlsx
+++ b/ids540_specific/class_schedule_540_xlsx.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids540_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F740E343-41D7-DA46-A2AC-12898471A7B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DCE5E0-0CFB-4748-A9C7-0D3823FE635C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="34560" windowHeight="19460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="class_schedule_590" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="104">
   <si>
     <t>Date, Rm</t>
   </si>
@@ -88,9 +88,6 @@
     <t>Wed, Sep 9</t>
   </si>
   <si>
-    <t>- Buffer Day</t>
-  </si>
-  <si>
     <t>- PPF3, Approaches to Testing. *Do do Coursera exercises in this section!*</t>
   </si>
   <si>
@@ -120,9 +117,6 @@
   </si>
   <si>
     <t>Wed, Sep 23</t>
-  </si>
-  <si>
-    <t>- More OOP</t>
   </si>
   <si>
     <t>Mon, Sep 28</t>
@@ -398,6 +392,15 @@
 - PPF2, Important Python Syntax
 - PPF2, Translating an Algorithm Into Python
 - `f-strings &lt;../notebooks/other/fstrings.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- Functions</t>
+  </si>
+  <si>
+    <t>- Black Jack Continued</t>
+  </si>
+  <si>
+    <t>- `Blackjack Extensions &lt;../exercises/exercise_blackjack_extensions&gt;`_</t>
   </si>
 </sst>
 </file>
@@ -833,7 +836,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D2" s="7"/>
     </row>
@@ -856,10 +859,10 @@
         <v>10</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -870,10 +873,10 @@
         <v>11</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -881,10 +884,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -892,12 +895,12 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>13</v>
@@ -911,7 +914,7 @@
     </row>
     <row r="9" spans="1:4" ht="118" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>17</v>
@@ -920,280 +923,280 @@
         <v>18</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>21</v>
-      </c>
       <c r="D10" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>97</v>
+        <v>102</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>98</v>
+        <v>22</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="136" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>99</v>
+        <v>25</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B14" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>31</v>
+      <c r="D14" s="11" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="170" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>35</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>47</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="106" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>51</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>55</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="85" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>59</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="134" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="103" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>67</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="105" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>73</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="85" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>77</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="105" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>81</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C30" s="11"/>
     </row>

--- a/ids540_specific/class_schedule_540_xlsx.xlsx
+++ b/ids540_specific/class_schedule_540_xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids540_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DCE5E0-0CFB-4748-A9C7-0D3823FE635C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{115D048C-C7E9-824D-B828-C341FD5A6742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -400,7 +400,7 @@
     <t>- Black Jack Continued</t>
   </si>
   <si>
-    <t>- `Blackjack Extensions &lt;../exercises/exercise_blackjack_extensions&gt;`_</t>
+    <t>- `Blackjack Extensions &lt;../exercises/exercise_blackjack_extensions.html&gt;`_</t>
   </si>
 </sst>
 </file>

--- a/ids540_specific/class_schedule_540_xlsx.xlsx
+++ b/ids540_specific/class_schedule_540_xlsx.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids540_specific/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vesper/Documents/GitHub/practicaldatascience_book/ids540_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{115D048C-C7E9-824D-B828-C341FD5A6742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7CE5677-63B3-794D-B974-7E376B7C3392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -371,9 +371,6 @@
     <t>- `Blackjack &lt;../exercises/exercise_blackjack.html&gt;`_</t>
   </si>
   <si>
-    <t>- `List Max &lt;../exercises/exercise_listmax.html&gt;`_</t>
-  </si>
-  <si>
     <t>- `HR Peak &lt;../exercises/exercise_hrpeak.html&gt;`_</t>
   </si>
   <si>
@@ -401,6 +398,10 @@
   </si>
   <si>
     <t>- `Blackjack Extensions &lt;../exercises/exercise_blackjack_extensions.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `List Max &lt;../exercises/exercise_listmax.html&gt;`_ 
+- `HR Peak &lt;../exercises/exercise_hrpeak.html&gt;`_</t>
   </si>
 </sst>
 </file>
@@ -509,9 +510,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -549,7 +550,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -655,7 +656,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -797,7 +798,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -873,7 +874,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>93</v>
@@ -923,7 +924,7 @@
         <v>18</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -931,7 +932,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>20</v>
@@ -945,10 +946,10 @@
         <v>29</v>
       </c>
       <c r="B11" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>102</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -962,7 +963,7 @@
         <v>23</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="136" customHeight="1" x14ac:dyDescent="0.2">
@@ -973,7 +974,7 @@
         <v>25</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.2">
@@ -987,7 +988,7 @@
         <v>28</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="170" customHeight="1" x14ac:dyDescent="0.2">
@@ -1001,7 +1002,7 @@
         <v>31</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">

--- a/ids540_specific/class_schedule_540_xlsx.xlsx
+++ b/ids540_specific/class_schedule_540_xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vesper/Documents/GitHub/practicaldatascience_book/ids540_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7CE5677-63B3-794D-B974-7E376B7C3392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC6B298A-24AE-BC45-A48C-7C2BDAC11E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ids540_specific/class_schedule_540_xlsx.xlsx
+++ b/ids540_specific/class_schedule_540_xlsx.xlsx
@@ -8,19 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vesper/Documents/GitHub/practicaldatascience_book/ids540_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC6B298A-24AE-BC45-A48C-7C2BDAC11E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8FFA9D0-6FD3-124C-9AF3-2CE39D1D5F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="960" yWindow="2260" windowWidth="30240" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="class_schedule_590" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="104">
   <si>
     <t>Date, Rm</t>
   </si>
@@ -103,17 +115,10 @@
     <t>Wed, Sep 16</t>
   </si>
   <si>
-    <t>- More Lists</t>
-  </si>
-  <si>
     <t>Mon, Sep 21</t>
   </si>
   <si>
     <t>- Object Oriented Programming</t>
-  </si>
-  <si>
-    <t>- `Join class session for next Coursera course with Duke email &lt;https://coursera.org/groups/numpy-data-science-kfkep/invitation&gt;`_
-- DSwithNSD1, Basics of Object Oriented Programming</t>
   </si>
   <si>
     <t>Wed, Sep 23</t>
@@ -371,9 +376,6 @@
     <t>- `Blackjack &lt;../exercises/exercise_blackjack.html&gt;`_</t>
   </si>
   <si>
-    <t>- `HR Peak &lt;../exercises/exercise_hrpeak.html&gt;`_</t>
-  </si>
-  <si>
     <t>- `Point &lt;../exercises/exercise_point.html&gt;`_
 - `Circle &lt;../exercises/exercise_circle.html&gt;`_</t>
   </si>
@@ -402,6 +404,17 @@
   <si>
     <t>- `List Max &lt;../exercises/exercise_listmax.html&gt;`_ 
 - `HR Peak &lt;../exercises/exercise_hrpeak.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- More Lists
+'-Object Oriented Programming</t>
+  </si>
+  <si>
+    <t>- `Join class session for next Coursera course (Data Science with…) with Duke email &lt;https://coursera.org/groups/numpy-data-science-kfkep/invitation&gt;`_
+- DSwithNSD1, Basics of Object Oriented Programming</t>
+  </si>
+  <si>
+    <t>- Object Oriented Programming Continued</t>
   </si>
 </sst>
 </file>
@@ -837,7 +850,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D2" s="7"/>
     </row>
@@ -860,10 +873,10 @@
         <v>10</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -874,10 +887,10 @@
         <v>11</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -885,10 +898,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -896,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -924,37 +937,37 @@
         <v>18</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>22</v>
@@ -963,241 +976,240 @@
         <v>23</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="136" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>95</v>
+        <v>30</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>96</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
     </row>
     <row r="15" spans="1:4" ht="170" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>45</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="106" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>49</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>53</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="85" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="134" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="103" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>65</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="105" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="85" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>75</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="105" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>79</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C30" s="11"/>
     </row>

--- a/ids540_specific/class_schedule_540_xlsx.xlsx
+++ b/ids540_specific/class_schedule_540_xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vesper/Documents/GitHub/practicaldatascience_book/ids540_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8FFA9D0-6FD3-124C-9AF3-2CE39D1D5F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D863D79E-D7AE-0546-B290-F8F0F928AD27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="960" yWindow="2260" windowWidth="30240" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ids540_specific/class_schedule_540_xlsx.xlsx
+++ b/ids540_specific/class_schedule_540_xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vesper/Documents/GitHub/practicaldatascience_book/ids540_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D863D79E-D7AE-0546-B290-F8F0F928AD27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28CF68D-1ED7-0043-AE68-EB547C0BD7C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="2260" windowWidth="30240" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38420" yWindow="600" windowWidth="30240" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="class_schedule_590" sheetId="1" r:id="rId1"/>
@@ -178,10 +178,6 @@
 - `Writing Good Notebooks &lt;https://dukemids.com/data_science_skills/writing_good_jupyter_notebooks.html&gt;`_</t>
   </si>
   <si>
-    <t>- `Ex 1 &lt;../exercises/exercise_numpy_viewcopies.html&gt;`_
-- (Finish other numpy)</t>
-  </si>
-  <si>
     <t>Mon, Oct 12 (Break)</t>
   </si>
   <si>
@@ -193,9 +189,6 @@
   <si>
     <t>- `Matrices — From Welcome through Review of Matrices &lt;../notebooks/class_2/week_3/00_welcome_to_week_3.html&gt;`_ (*see navigation bar on left*)
 - `Arrays — From Welcome through Color Images as Arrays &lt;../notebooks/class_2/week_3/40_nd_arrays.html&gt;`_ (*see navigation bar on left*)</t>
-  </si>
-  <si>
-    <t>- `Ex 1 &lt;../exercises/90_remote_sensing.html&gt;`_</t>
   </si>
   <si>
     <t>Mon, Oct 19</t>
@@ -207,9 +200,6 @@
     <t>- `Speed / Ease of Use Tradeoff &lt;../notebooks/class_2/week_4/10_speed_and_ease_of_use.html&gt;`_
 - `Vectorization &lt;../notebooks/class_2/week_4/11_vectorization.html&gt;`_
 - Under Pandas, Read from `From Working with Tabular Data &lt;../notebooks/class_3/week_2/00_intro_to_pandas.html&gt;`_ through `Subsetting and Indexing with Single Square Brackets &lt;../notebooks/class_3/week_2/16_indexing_with_brackets.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `Link &lt;../exercises/exercise_series.html&gt;`_</t>
   </si>
   <si>
     <t>Wed, Oct 21</t>
@@ -224,9 +214,6 @@
 - `PyArrow Backend &lt;../notebooks/class_3/week_2/50_pandas_pyarrow.html&gt;`_</t>
   </si>
   <si>
-    <t>- `Link &lt;../exercises/exercise_dataframes.html&gt;`_</t>
-  </si>
-  <si>
     <t>Mon, Oct 26</t>
   </si>
   <si>
@@ -239,10 +226,6 @@
 - `Missing Data &lt;../notebooks/class_3/week_3/35_cleaning_missing_data.html&gt;`_</t>
   </si>
   <si>
-    <t>- `Link 1 &lt;../exercises/exercise_indices.html&gt;`_
-- `Link 2 &lt;../exercises/exercise_missing.html&gt;`_</t>
-  </si>
-  <si>
     <t>Wed, Oct 28</t>
   </si>
   <si>
@@ -273,9 +256,6 @@
   </si>
   <si>
     <t>Wed, Nov 4</t>
-  </si>
-  <si>
-    <t>- Groupby Continued</t>
   </si>
   <si>
     <t>Mon, Nov 9</t>
@@ -415,6 +395,27 @@
   </si>
   <si>
     <t>- Object Oriented Programming Continued</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- (Finish other numpy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- `View Copies &lt;../exercises/exercise_numpy_viewcopies.html&gt;`_
+</t>
+  </si>
+  <si>
+    <t>- `Remote Sensing &lt;../exercises/90_remote_sensing.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Series &lt;../exercises/exercise_series.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Dataframes &lt;../exercises/exercise_dataframes.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Ex. 1 Indices &lt;../exercises/exercise_indices.html&gt;`_
+- `Ex. 2 Missing &lt;../exercises/exercise_missing.html&gt;`_</t>
   </si>
 </sst>
 </file>
@@ -850,7 +851,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D2" s="7"/>
     </row>
@@ -873,10 +874,10 @@
         <v>10</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -887,10 +888,10 @@
         <v>11</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -898,10 +899,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -909,7 +910,7 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -937,7 +938,7 @@
         <v>18</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -945,13 +946,13 @@
         <v>25</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -959,10 +960,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -976,7 +977,7 @@
         <v>23</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="136" customHeight="1" x14ac:dyDescent="0.2">
@@ -984,13 +985,13 @@
         <v>30</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.2">
@@ -998,7 +999,7 @@
         <v>34</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -1014,20 +1015,20 @@
         <v>29</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" t="s">
         <v>41</v>
-      </c>
-      <c r="B16" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -1041,7 +1042,7 @@
     </row>
     <row r="18" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>35</v>
@@ -1053,9 +1054,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="160" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>35</v>
@@ -1064,152 +1065,152 @@
         <v>39</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>40</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>45</v>
+        <v>35</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="106" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>49</v>
+        <v>42</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="85" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>57</v>
+        <v>49</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="134" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>61</v>
+        <v>52</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="103" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="105" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="85" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="105" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="13" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C30" s="11"/>
     </row>

--- a/ids540_specific/class_schedule_540_xlsx.xlsx
+++ b/ids540_specific/class_schedule_540_xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vesper/Documents/GitHub/practicaldatascience_book/ids540_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28CF68D-1ED7-0043-AE68-EB547C0BD7C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8663EF7-F071-C541-AC34-4ADB73027EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38420" yWindow="600" windowWidth="30240" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="960" yWindow="2260" windowWidth="30240" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="class_schedule_590" sheetId="1" r:id="rId1"/>
@@ -237,9 +237,6 @@
 - `Datacamp Class "Regular Expressions for Pattern Matching," Chapter 3 (Introduction to regular expressions) &lt;https://campus.datacamp.com/courses/regular-expressions-in-python/basic-concepts-of-string-manipulation?ex=1&gt;`_</t>
   </si>
   <si>
-    <t>- `Link &lt;../exercises/exercise_cleaning.html&gt;`_</t>
-  </si>
-  <si>
     <t>Mon, Nov 2</t>
   </si>
   <si>
@@ -249,10 +246,6 @@
   <si>
     <t>- Defensive Programming: from `first reading &lt;../notebooks/PDS_not_yet_in_coursera/20_programming_concepts/defensive_programming.html&gt;`_ through `Iceberg Principle &lt;../notebooks/PDS_not_yet_in_coursera/20_programming_concepts/iceberg_principle.html&gt;`_
 - `Groupby &lt;../notebooks/class_3/week_4/20_grouping.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `Link &lt;../exercises/exercise_groupby.html&gt;`_
-- `Opioids Project &lt;https://github.com/nickeubank/practicaldatascience_book/blob/main/ids590_specific/opioids_590/PDS590_ProjectSummary.pdf&gt;`_</t>
   </si>
   <si>
     <t>Wed, Nov 4</t>
@@ -272,9 +265,6 @@
 - `Merge Validation &lt;../notebooks/class_3/week_4/15.3_validating_a_merge.html&gt;`_</t>
   </si>
   <si>
-    <t>- `Link &lt;../exercises/exercise_merging.html&gt;`_</t>
-  </si>
-  <si>
     <t>Wed, Nov 11</t>
   </si>
   <si>
@@ -287,9 +277,6 @@
 - `Explicit v Implict &lt;../notebooks/class_5/week_1/1.4.5_explicit_vs_implicit_syntax.html&gt;`_
 - `Saving Plots &lt;../notebooks/class_5/week_1/1.4.4_saving_to_file.html&gt;`_
 - `Using LLMs Well &lt;../notebooks/PDS_not_yet_in_coursera/99_advice/using_llms_well.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `Link &lt;../exercises/exercise_plotting_part1.html&gt;`_</t>
   </si>
   <si>
     <t>Mon, Nov 16</t>
@@ -307,9 +294,6 @@
 - `Pandas Plotting &lt;../notebooks/class_5/week_1/1.6.1_plotting_with_pandas.html&gt;`_</t>
   </si>
   <si>
-    <t>- `Link &lt;../exercises/exercise_plotting_part2.html&gt;`_</t>
-  </si>
-  <si>
     <t>Wed, Nov 18</t>
   </si>
   <si>
@@ -416,6 +400,21 @@
   <si>
     <t>- `Ex. 1 Indices &lt;../exercises/exercise_indices.html&gt;`_
 - `Ex. 2 Missing &lt;../exercises/exercise_missing.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Cleaning &lt;../exercises/exercise_cleaning.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Groupby &lt;../exercises/exercise_groupby.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Merging &lt;../exercises/exercise_merging.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Plotting (Part 1) &lt;../exercises/exercise_plotting_part1.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Plotting (Part 2) &lt;../exercises/exercise_plotting_part2.html&gt;`_</t>
   </si>
 </sst>
 </file>
@@ -851,7 +850,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D2" s="7"/>
     </row>
@@ -874,10 +873,10 @@
         <v>10</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -888,10 +887,10 @@
         <v>11</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -899,10 +898,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -910,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -938,7 +937,7 @@
         <v>18</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -946,13 +945,13 @@
         <v>25</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -960,10 +959,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -977,7 +976,7 @@
         <v>23</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="136" customHeight="1" x14ac:dyDescent="0.2">
@@ -985,13 +984,13 @@
         <v>30</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.2">
@@ -999,7 +998,7 @@
         <v>34</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -1015,7 +1014,7 @@
         <v>29</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -1028,7 +1027,7 @@
     </row>
     <row r="17" spans="1:4" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -1065,7 +1064,7 @@
         <v>39</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -1076,7 +1075,7 @@
         <v>35</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="106" customHeight="1" x14ac:dyDescent="0.2">
@@ -1090,12 +1089,12 @@
         <v>43</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>45</v>
@@ -1104,12 +1103,12 @@
         <v>46</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="85" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>48</v>
@@ -1118,12 +1117,12 @@
         <v>49</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="134" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>51</v>
@@ -1132,12 +1131,12 @@
         <v>52</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="103" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>54</v>
@@ -1146,71 +1145,71 @@
         <v>55</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="105" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>59</v>
-      </c>
       <c r="D26" s="7" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="85" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="105" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="13" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C30" s="11"/>
     </row>

--- a/ids540_specific/class_schedule_540_xlsx.xlsx
+++ b/ids540_specific/class_schedule_540_xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vesper/Documents/GitHub/practicaldatascience_book/ids540_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8663EF7-F071-C541-AC34-4ADB73027EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D6E611-B0DD-724F-9DB3-A0F52B1075E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="960" yWindow="2260" windowWidth="30240" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -385,13 +385,6 @@
 - (Finish other numpy)</t>
   </si>
   <si>
-    <t xml:space="preserve">- `View Copies &lt;../exercises/exercise_numpy_viewcopies.html&gt;`_
-</t>
-  </si>
-  <si>
-    <t>- `Remote Sensing &lt;../exercises/90_remote_sensing.html&gt;`_</t>
-  </si>
-  <si>
     <t>- `Series &lt;../exercises/exercise_series.html&gt;`_</t>
   </si>
   <si>
@@ -415,6 +408,13 @@
   </si>
   <si>
     <t>- `Plotting (Part 2) &lt;../exercises/exercise_plotting_part2.html&gt;`_</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - `Remote Sensing &lt;../exercises/exercise_remote_sensing.html&gt;`_</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -`Opioids Project' &lt;../ids540_specific/opioids_540/PDS590_ProjectSummary.pdf&gt;`
+</t>
   </si>
 </sst>
 </file>
@@ -1075,7 +1075,7 @@
         <v>35</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="106" customHeight="1" x14ac:dyDescent="0.2">
@@ -1089,7 +1089,7 @@
         <v>43</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="140" customHeight="1" x14ac:dyDescent="0.2">
@@ -1103,7 +1103,7 @@
         <v>46</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="85" x14ac:dyDescent="0.2">
@@ -1117,7 +1117,7 @@
         <v>49</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="134" customHeight="1" x14ac:dyDescent="0.2">
@@ -1131,7 +1131,7 @@
         <v>52</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="103" customHeight="1" x14ac:dyDescent="0.2">
@@ -1145,7 +1145,7 @@
         <v>55</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="105" customHeight="1" x14ac:dyDescent="0.2">
@@ -1159,7 +1159,7 @@
         <v>58</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43" customHeight="1" x14ac:dyDescent="0.2">
@@ -1173,7 +1173,7 @@
         <v>62</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="85" x14ac:dyDescent="0.2">
@@ -1187,7 +1187,7 @@
         <v>65</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="105" x14ac:dyDescent="0.2">
@@ -1201,7 +1201,7 @@
         <v>68</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">

--- a/ids540_specific/class_schedule_540_xlsx.xlsx
+++ b/ids540_specific/class_schedule_540_xlsx.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vesper/Documents/GitHub/practicaldatascience_book/ids540_specific/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nce8/github/practicaldatascience_book/ids540_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D6E611-B0DD-724F-9DB3-A0F52B1075E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1F2F35-4F34-FD4D-B298-6B1D45973AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="960" yWindow="2260" windowWidth="30240" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -303,118 +303,118 @@
     <t>Final project due date</t>
   </si>
   <si>
-    <t>- **SETUP 1:** `Installing Python and miniconda &lt;../notebooks/PDS_not_yet_in_coursera/00_setup_env/setup_python.html&gt;`_
+    <t>- Legos Day 2</t>
+  </si>
+  <si>
+    <t>- More time with legos</t>
+  </si>
+  <si>
+    <t>Wed, Oct 14</t>
+  </si>
+  <si>
+    <t>LABOR DAY</t>
+  </si>
+  <si>
+    <t>Mon, Nov 23rd</t>
+  </si>
+  <si>
+    <t>Wed, Nov 25th</t>
+  </si>
+  <si>
+    <t>More time on Max and Triangle</t>
+  </si>
+  <si>
+    <t>- Using VS Code
+- `Max &lt;../exercises/exercise_max.html&gt;`_
+- `Triangle &lt;../exercises/exercise_triangle.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Blackjack &lt;../exercises/exercise_blackjack.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Point &lt;../exercises/exercise_point.html&gt;`_
+- `Circle &lt;../exercises/exercise_circle.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Count Words &lt;../exercises/exercise_countwords.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Debugging &lt;../exercises/exercise_debugger540.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `chatGPT and You &lt;https://dukemids.com/data_science_skills/llms.html&gt;`_
+- PPF1, Data Types
+- PPF2, Important Python Syntax
+- PPF2, Translating an Algorithm Into Python
+- `f-strings &lt;../notebooks/other/fstrings.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- Functions</t>
+  </si>
+  <si>
+    <t>- Black Jack Continued</t>
+  </si>
+  <si>
+    <t>- `Blackjack Extensions &lt;../exercises/exercise_blackjack_extensions.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `List Max &lt;../exercises/exercise_listmax.html&gt;`_ 
+- `HR Peak &lt;../exercises/exercise_hrpeak.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- More Lists
+'-Object Oriented Programming</t>
+  </si>
+  <si>
+    <t>- `Join class session for next Coursera course (Data Science with…) with Duke email &lt;https://coursera.org/groups/numpy-data-science-kfkep/invitation&gt;`_
+- DSwithNSD1, Basics of Object Oriented Programming</t>
+  </si>
+  <si>
+    <t>- Object Oriented Programming Continued</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- (Finish other numpy)</t>
+  </si>
+  <si>
+    <t>- `Series &lt;../exercises/exercise_series.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Dataframes &lt;../exercises/exercise_dataframes.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Ex. 1 Indices &lt;../exercises/exercise_indices.html&gt;`_
+- `Ex. 2 Missing &lt;../exercises/exercise_missing.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Cleaning &lt;../exercises/exercise_cleaning.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Groupby &lt;../exercises/exercise_groupby.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Merging &lt;../exercises/exercise_merging.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Plotting (Part 1) &lt;../exercises/exercise_plotting_part1.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Plotting (Part 2) &lt;../exercises/exercise_plotting_part2.html&gt;`_</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - `Remote Sensing &lt;../exercises/exercise_remote_sensing.html&gt;`_</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -`Opioids Project' &lt;../ids540_specific/opioids_540/PDS590_ProjectSummary.pdf&gt;`
+</t>
+  </si>
+  <si>
+    <t>- **SETUP 1:** `Installing Python and miniforge &lt;../notebooks/PDS_not_yet_in_coursera/00_setup_env/setup_python.html&gt;`_
 - **SETUP 2:** `Installing and Configuring VS Code &lt;../notebooks/PDS_not_yet_in_coursera/00_setup_env/setup_vscode.html&gt;`_
 - `Read and sign syllabus, submit on gradescope &lt;https://github.com/nickeubank/practicaldatascience_book/blob/main/ids540_specific/syllabus_540/Syllabus_IDS540.pdf&gt;`_
 - `Register with IPUMS &lt;https://uma.pop.umn.edu/usa/user/new&gt;`_
 - `Register for DataCamp (duke.edu address required) &lt;https://www.datacamp.com/groups/shared_links/2d3263feebc26e4a9d40f8123d4878006b4969fe3063758f0ae599e2162c4d40&gt;`_
 - `Join Coursera IDS 540 Session of Python Programming Fundamentals &lt;https://coursera.org/groups/python-programming-fundamentals-ywjfc/invitation&gt;`_</t>
-  </si>
-  <si>
-    <t>- Legos Day 2</t>
-  </si>
-  <si>
-    <t>- More time with legos</t>
-  </si>
-  <si>
-    <t>Wed, Oct 14</t>
-  </si>
-  <si>
-    <t>LABOR DAY</t>
-  </si>
-  <si>
-    <t>Mon, Nov 23rd</t>
-  </si>
-  <si>
-    <t>Wed, Nov 25th</t>
-  </si>
-  <si>
-    <t>More time on Max and Triangle</t>
-  </si>
-  <si>
-    <t>- Using VS Code
-- `Max &lt;../exercises/exercise_max.html&gt;`_
-- `Triangle &lt;../exercises/exercise_triangle.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `Blackjack &lt;../exercises/exercise_blackjack.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `Point &lt;../exercises/exercise_point.html&gt;`_
-- `Circle &lt;../exercises/exercise_circle.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `Count Words &lt;../exercises/exercise_countwords.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `Debugging &lt;../exercises/exercise_debugger540.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `chatGPT and You &lt;https://dukemids.com/data_science_skills/llms.html&gt;`_
-- PPF1, Data Types
-- PPF2, Important Python Syntax
-- PPF2, Translating an Algorithm Into Python
-- `f-strings &lt;../notebooks/other/fstrings.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- Functions</t>
-  </si>
-  <si>
-    <t>- Black Jack Continued</t>
-  </si>
-  <si>
-    <t>- `Blackjack Extensions &lt;../exercises/exercise_blackjack_extensions.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `List Max &lt;../exercises/exercise_listmax.html&gt;`_ 
-- `HR Peak &lt;../exercises/exercise_hrpeak.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- More Lists
-'-Object Oriented Programming</t>
-  </si>
-  <si>
-    <t>- `Join class session for next Coursera course (Data Science with…) with Duke email &lt;https://coursera.org/groups/numpy-data-science-kfkep/invitation&gt;`_
-- DSwithNSD1, Basics of Object Oriented Programming</t>
-  </si>
-  <si>
-    <t>- Object Oriented Programming Continued</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-- (Finish other numpy)</t>
-  </si>
-  <si>
-    <t>- `Series &lt;../exercises/exercise_series.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `Dataframes &lt;../exercises/exercise_dataframes.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `Ex. 1 Indices &lt;../exercises/exercise_indices.html&gt;`_
-- `Ex. 2 Missing &lt;../exercises/exercise_missing.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `Cleaning &lt;../exercises/exercise_cleaning.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `Groupby &lt;../exercises/exercise_groupby.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `Merging &lt;../exercises/exercise_merging.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `Plotting (Part 1) &lt;../exercises/exercise_plotting_part1.html&gt;`_</t>
-  </si>
-  <si>
-    <t>- `Plotting (Part 2) &lt;../exercises/exercise_plotting_part2.html&gt;`_</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - `Remote Sensing &lt;../exercises/exercise_remote_sensing.html&gt;`_</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -`Opioids Project' &lt;../ids540_specific/opioids_540/PDS590_ProjectSummary.pdf&gt;`
-</t>
   </si>
 </sst>
 </file>
@@ -523,9 +523,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -563,7 +563,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -669,7 +669,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -811,7 +811,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -850,7 +850,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="D2" s="7"/>
     </row>
@@ -873,10 +873,10 @@
         <v>10</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>73</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -887,10 +887,10 @@
         <v>11</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -898,10 +898,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -909,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -937,7 +937,7 @@
         <v>18</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -945,13 +945,13 @@
         <v>25</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -959,10 +959,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>87</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -976,7 +976,7 @@
         <v>23</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="136" customHeight="1" x14ac:dyDescent="0.2">
@@ -984,13 +984,13 @@
         <v>30</v>
       </c>
       <c r="B13" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>91</v>
-      </c>
       <c r="D13" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.2">
@@ -998,7 +998,7 @@
         <v>34</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -1014,7 +1014,7 @@
         <v>29</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -1027,7 +1027,7 @@
     </row>
     <row r="17" spans="1:4" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -1064,7 +1064,7 @@
         <v>39</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -1075,7 +1075,7 @@
         <v>35</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="106" customHeight="1" x14ac:dyDescent="0.2">
@@ -1089,7 +1089,7 @@
         <v>43</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="140" customHeight="1" x14ac:dyDescent="0.2">
@@ -1103,7 +1103,7 @@
         <v>46</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="85" x14ac:dyDescent="0.2">
@@ -1117,7 +1117,7 @@
         <v>49</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="134" customHeight="1" x14ac:dyDescent="0.2">
@@ -1131,7 +1131,7 @@
         <v>52</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="103" customHeight="1" x14ac:dyDescent="0.2">
@@ -1145,7 +1145,7 @@
         <v>55</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="105" customHeight="1" x14ac:dyDescent="0.2">
@@ -1159,7 +1159,7 @@
         <v>58</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43" customHeight="1" x14ac:dyDescent="0.2">
@@ -1173,12 +1173,12 @@
         <v>62</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="85" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>64</v>
@@ -1187,12 +1187,12 @@
         <v>65</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="105" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>67</v>
@@ -1201,7 +1201,7 @@
         <v>68</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">

--- a/ids540_specific/class_schedule_540_xlsx.xlsx
+++ b/ids540_specific/class_schedule_540_xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vesper/Documents/GitHub/practicaldatascience_book/ids540_specific/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D6E611-B0DD-724F-9DB3-A0F52B1075E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED5C985-6CB4-8B46-893E-BD7E2F59D13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="2260" windowWidth="30240" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35640" yWindow="1260" windowWidth="30240" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="class_schedule_590" sheetId="1" r:id="rId1"/>
@@ -163,9 +163,6 @@
 - `Python v. R &lt;../notebooks/PDS_not_yet_in_coursera/20_programming_concepts/python_v_r.html&gt;`_</t>
   </si>
   <si>
-    <t>- `Ex 1 &lt;../exercises/exercise_numpy_vectors.html&gt;`_</t>
-  </si>
-  <si>
     <t>Wed, Oct 7</t>
   </si>
   <si>
@@ -413,8 +410,12 @@
     <t xml:space="preserve"> - `Remote Sensing &lt;../exercises/exercise_remote_sensing.html&gt;`_</t>
   </si>
   <si>
-    <t xml:space="preserve"> -`Opioids Project' &lt;../ids540_specific/opioids_540/PDS590_ProjectSummary.pdf&gt;`
-</t>
+    <t xml:space="preserve"> -`Opioids Project' &lt;../ids540_specific/opioids_540/PDS590_ProjectSummary.pdf&gt;`_
+ -`Template' &lt;../ids540_specific/opioids_540/PracticalDataScience_BackwardsDesignTemplate.pdf&gt;`_
+ - `Numpy Views Copies &lt;../exercises/exercise_numpy_viewscopies.html&gt;`_</t>
+  </si>
+  <si>
+    <t>- `Numpy Vectors (Ineq) &lt;../exercises/exercise_numpy_vectors.html&gt;`_</t>
   </si>
 </sst>
 </file>
@@ -850,7 +851,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D2" s="7"/>
     </row>
@@ -873,10 +874,10 @@
         <v>10</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>73</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -887,10 +888,10 @@
         <v>11</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -898,10 +899,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -909,7 +910,7 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -937,7 +938,7 @@
         <v>18</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -945,13 +946,13 @@
         <v>25</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -959,10 +960,10 @@
         <v>27</v>
       </c>
       <c r="B11" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>87</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
@@ -976,7 +977,7 @@
         <v>23</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="136" customHeight="1" x14ac:dyDescent="0.2">
@@ -984,13 +985,13 @@
         <v>30</v>
       </c>
       <c r="B13" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>91</v>
-      </c>
       <c r="D13" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.2">
@@ -998,14 +999,14 @@
         <v>34</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
     </row>
     <row r="15" spans="1:4" ht="170" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>26</v>
@@ -1014,20 +1015,20 @@
         <v>29</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
         <v>40</v>
-      </c>
-      <c r="B16" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -1041,7 +1042,7 @@
     </row>
     <row r="18" spans="1:4" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>35</v>
@@ -1050,166 +1051,166 @@
         <v>36</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="160" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="106" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="11" t="s">
-        <v>43</v>
-      </c>
       <c r="D21" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="D22" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="85" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="D23" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="134" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B24" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="D24" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="103" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="D25" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="105" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>58</v>
-      </c>
       <c r="D26" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="11" t="s">
-        <v>62</v>
-      </c>
       <c r="D27" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="85" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="D28" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="105" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="7" t="s">
-        <v>68</v>
-      </c>
       <c r="D29" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="14" t="s">
         <v>70</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>71</v>
       </c>
       <c r="C30" s="11"/>
     </row>
